--- a/ONI.xlsx
+++ b/ONI.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Andres_Tobon\Desktop\Proyecto_Pronostico precios\Datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B012F78-AE3B-4AB6-9C4C-5ACCE6BD1D7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CD19772-F9F3-49D5-A910-83848B3EAE5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -379,7 +379,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F78"/>
+  <dimension ref="A1:F80"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="18" style="1" bestFit="1" customWidth="1"/>
@@ -435,7 +435,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1">
-        <v>43831</v>
+        <v>46174</v>
       </c>
       <c r="B7">
         <v>0.5</v>
@@ -443,87 +443,87 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1">
-        <v>43862</v>
+        <v>46204</v>
       </c>
       <c r="B8">
-        <v>0.4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1">
-        <v>43891</v>
+        <v>43831</v>
       </c>
       <c r="B9">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1">
-        <v>43922</v>
+        <v>43862</v>
       </c>
       <c r="B10">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1">
-        <v>43952</v>
+        <v>43891</v>
       </c>
       <c r="B11">
-        <v>-0.2</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1">
-        <v>43983</v>
+        <v>43922</v>
       </c>
       <c r="B12">
-        <v>-0.5</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1">
-        <v>44013</v>
+        <v>43952</v>
       </c>
       <c r="B13">
-        <v>-0.8</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1">
-        <v>44044</v>
+        <v>43983</v>
       </c>
       <c r="B14">
-        <v>-1</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1">
-        <v>44075</v>
+        <v>44013</v>
       </c>
       <c r="B15">
-        <v>-1.2</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1">
-        <v>44105</v>
+        <v>44044</v>
       </c>
       <c r="B16">
-        <v>-1.3</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1">
-        <v>44136</v>
+        <v>44075</v>
       </c>
       <c r="B17">
-        <v>-1.4</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1">
-        <v>44166</v>
+        <v>44105</v>
       </c>
       <c r="B18">
         <v>-1.3</v>
@@ -531,103 +531,103 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1">
-        <v>44197</v>
+        <v>44136</v>
       </c>
       <c r="B19">
-        <v>-1.2</v>
+        <v>-1.4</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1">
-        <v>44228</v>
+        <v>44166</v>
       </c>
       <c r="B20">
-        <v>-1.1000000000000001</v>
+        <v>-1.3</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1">
-        <v>44256</v>
+        <v>44197</v>
       </c>
       <c r="B21">
-        <v>-0.8</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1">
-        <v>44287</v>
+        <v>44228</v>
       </c>
       <c r="B22">
-        <v>-0.5</v>
+        <v>-1.1000000000000001</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1">
-        <v>44317</v>
+        <v>44256</v>
       </c>
       <c r="B23">
-        <v>-0.3</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1">
-        <v>44348</v>
+        <v>44287</v>
       </c>
       <c r="B24">
-        <v>-0.1</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1">
-        <v>44378</v>
+        <v>44317</v>
       </c>
       <c r="B25">
-        <v>-0.2</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1">
-        <v>44409</v>
+        <v>44348</v>
       </c>
       <c r="B26">
-        <v>-0.4</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1">
-        <v>44440</v>
+        <v>44378</v>
       </c>
       <c r="B27">
-        <v>-0.7</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1">
-        <v>44470</v>
+        <v>44409</v>
       </c>
       <c r="B28">
-        <v>-0.9</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1">
-        <v>44501</v>
+        <v>44440</v>
       </c>
       <c r="B29">
-        <v>-1</v>
+        <v>-0.7</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1">
-        <v>44531</v>
+        <v>44470</v>
       </c>
       <c r="B30">
-        <v>-1</v>
+        <v>-0.9</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1">
-        <v>44562</v>
+        <v>44501</v>
       </c>
       <c r="B31">
         <v>-1</v>
@@ -635,7 +635,7 @@
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1">
-        <v>44593</v>
+        <v>44531</v>
       </c>
       <c r="B32">
         <v>-1</v>
@@ -643,39 +643,39 @@
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1">
-        <v>44621</v>
+        <v>44562</v>
       </c>
       <c r="B33">
-        <v>-0.9</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1">
-        <v>44652</v>
+        <v>44593</v>
       </c>
       <c r="B34">
-        <v>-0.9</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1">
-        <v>44682</v>
+        <v>44621</v>
       </c>
       <c r="B35">
-        <v>-1</v>
+        <v>-0.9</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1">
-        <v>44713</v>
+        <v>44652</v>
       </c>
       <c r="B36">
-        <v>-1</v>
+        <v>-0.9</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1">
-        <v>44743</v>
+        <v>44682</v>
       </c>
       <c r="B37">
         <v>-1</v>
@@ -683,7 +683,7 @@
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1">
-        <v>44774</v>
+        <v>44713</v>
       </c>
       <c r="B38">
         <v>-1</v>
@@ -691,7 +691,7 @@
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1">
-        <v>44805</v>
+        <v>44743</v>
       </c>
       <c r="B39">
         <v>-1</v>
@@ -699,318 +699,334 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1">
-        <v>44835</v>
+        <v>44774</v>
       </c>
       <c r="B40">
-        <v>-1.1000000000000001</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1">
-        <v>44866</v>
+        <v>44805</v>
       </c>
       <c r="B41">
-        <v>-1.2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1">
-        <v>44896</v>
+        <v>44835</v>
       </c>
       <c r="B42">
-        <v>-1</v>
+        <v>-1.1000000000000001</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1">
-        <v>44927</v>
+        <v>44866</v>
       </c>
       <c r="B43">
-        <v>-0.8</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1">
-        <v>44958</v>
+        <v>44896</v>
       </c>
       <c r="B44">
-        <v>-0.6</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1">
-        <v>44986</v>
+        <v>44927</v>
       </c>
       <c r="B45">
-        <v>-0.3</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1">
-        <v>45017</v>
+        <v>44958</v>
       </c>
       <c r="B46">
-        <v>0.1</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1">
-        <v>45047</v>
+        <v>44986</v>
       </c>
       <c r="B47">
-        <v>0.5</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1">
+        <v>45017</v>
+      </c>
+      <c r="B48">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49" s="1">
+        <v>45047</v>
+      </c>
+      <c r="B49">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50" s="1">
         <v>45078</v>
       </c>
-      <c r="B48">
+      <c r="B50">
         <v>0.9</v>
       </c>
     </row>
-    <row r="49" spans="1:6">
-      <c r="A49" s="1">
+    <row r="51" spans="1:2">
+      <c r="A51" s="1">
         <v>45108</v>
       </c>
-      <c r="B49">
+      <c r="B51">
         <v>1.2</v>
       </c>
     </row>
-    <row r="50" spans="1:6">
-      <c r="A50" s="1">
+    <row r="52" spans="1:2">
+      <c r="A52" s="1">
         <v>45139</v>
       </c>
-      <c r="B50">
+      <c r="B52">
         <v>1.5</v>
       </c>
     </row>
-    <row r="51" spans="1:6">
-      <c r="A51" s="1">
+    <row r="53" spans="1:2">
+      <c r="A53" s="1">
         <v>45170</v>
       </c>
-      <c r="B51">
+      <c r="B53">
         <v>1.8</v>
       </c>
     </row>
-    <row r="52" spans="1:6">
-      <c r="A52" s="1">
+    <row r="54" spans="1:2">
+      <c r="A54" s="1">
         <v>45200</v>
       </c>
-      <c r="B52">
+      <c r="B54">
         <v>2</v>
       </c>
     </row>
-    <row r="53" spans="1:6">
-      <c r="A53" s="1">
+    <row r="55" spans="1:2">
+      <c r="A55" s="1">
         <v>45231</v>
       </c>
-      <c r="B53">
+      <c r="B55">
         <v>2</v>
       </c>
     </row>
-    <row r="54" spans="1:6">
-      <c r="A54" s="1">
+    <row r="56" spans="1:2">
+      <c r="A56" s="1">
         <v>45261</v>
       </c>
-      <c r="B54">
+      <c r="B56">
         <v>1.9</v>
       </c>
     </row>
-    <row r="55" spans="1:6">
-      <c r="A55" s="1">
+    <row r="57" spans="1:2">
+      <c r="A57" s="1">
         <v>45292</v>
       </c>
-      <c r="B55">
+      <c r="B57">
         <v>1.7</v>
       </c>
     </row>
-    <row r="56" spans="1:6">
-      <c r="A56" s="1">
+    <row r="58" spans="1:2">
+      <c r="A58" s="1">
         <v>45323</v>
       </c>
-      <c r="B56">
+      <c r="B58">
         <v>1.4</v>
       </c>
     </row>
-    <row r="57" spans="1:6">
-      <c r="A57" s="1">
+    <row r="59" spans="1:2">
+      <c r="A59" s="1">
         <v>45352</v>
       </c>
-      <c r="B57">
+      <c r="B59">
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="58" spans="1:6">
-      <c r="A58" s="1">
+    <row r="60" spans="1:2">
+      <c r="A60" s="1">
         <v>45383</v>
       </c>
-      <c r="B58">
+      <c r="B60">
         <v>0.7</v>
       </c>
     </row>
-    <row r="59" spans="1:6">
-      <c r="A59" s="1">
+    <row r="61" spans="1:2">
+      <c r="A61" s="1">
         <v>45413</v>
       </c>
-      <c r="B59">
+      <c r="B61">
         <v>0.4</v>
       </c>
     </row>
-    <row r="60" spans="1:6">
-      <c r="A60" s="1">
+    <row r="62" spans="1:2">
+      <c r="A62" s="1">
         <v>45444</v>
       </c>
-      <c r="B60">
+      <c r="B62">
         <v>0.1</v>
       </c>
     </row>
-    <row r="61" spans="1:6">
-      <c r="A61" s="1">
+    <row r="63" spans="1:2">
+      <c r="A63" s="1">
         <v>45474</v>
       </c>
-      <c r="B61">
+      <c r="B63">
         <v>-0.2</v>
       </c>
     </row>
-    <row r="62" spans="1:6">
-      <c r="A62" s="1">
+    <row r="64" spans="1:2">
+      <c r="A64" s="1">
         <v>45505</v>
       </c>
-      <c r="B62">
+      <c r="B64">
         <v>-0.4</v>
       </c>
-    </row>
-    <row r="63" spans="1:6">
-      <c r="A63" s="1">
-        <v>45536</v>
-      </c>
-      <c r="B63">
-        <v>-0.5</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6">
-      <c r="A64" s="1">
-        <v>45566</v>
-      </c>
-      <c r="B64">
-        <v>-0.5</v>
-      </c>
-      <c r="F64" s="2"/>
     </row>
     <row r="65" spans="1:6">
       <c r="A65" s="1">
-        <v>45597</v>
+        <v>45536</v>
       </c>
       <c r="B65">
         <v>-0.5</v>
       </c>
-      <c r="F65" s="2"/>
     </row>
     <row r="66" spans="1:6">
       <c r="A66" s="1">
-        <v>45627</v>
+        <v>45566</v>
       </c>
       <c r="B66">
-        <v>-0.4</v>
+        <v>-0.5</v>
       </c>
       <c r="F66" s="2"/>
     </row>
     <row r="67" spans="1:6">
       <c r="A67" s="1">
-        <v>45658</v>
+        <v>45597</v>
       </c>
       <c r="B67">
-        <v>-0.3</v>
+        <v>-0.5</v>
       </c>
       <c r="F67" s="2"/>
     </row>
     <row r="68" spans="1:6">
       <c r="A68" s="1">
-        <v>45689</v>
+        <v>45627</v>
       </c>
       <c r="B68">
-        <v>-0.2</v>
+        <v>-0.4</v>
       </c>
       <c r="F68" s="2"/>
     </row>
     <row r="69" spans="1:6">
       <c r="A69" s="1">
-        <v>45717</v>
+        <v>45658</v>
       </c>
       <c r="B69">
-        <v>-0.1</v>
-      </c>
+        <v>-0.3</v>
+      </c>
+      <c r="F69" s="2"/>
     </row>
     <row r="70" spans="1:6">
       <c r="A70" s="1">
-        <v>45748</v>
+        <v>45689</v>
       </c>
       <c r="B70">
-        <v>0</v>
-      </c>
+        <v>-0.2</v>
+      </c>
+      <c r="F70" s="2"/>
     </row>
     <row r="71" spans="1:6">
       <c r="A71" s="1">
-        <v>45778</v>
+        <v>45717</v>
       </c>
       <c r="B71">
-        <v>0.1</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="72" spans="1:6">
       <c r="A72" s="1">
-        <v>45809</v>
+        <v>45748</v>
       </c>
       <c r="B72">
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="1">
-        <v>45839</v>
+        <v>45778</v>
       </c>
       <c r="B73">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="1">
-        <v>45870</v>
+        <v>45809</v>
       </c>
       <c r="B74">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="75" spans="1:6">
       <c r="A75" s="1">
-        <v>45901</v>
+        <v>45839</v>
       </c>
       <c r="B75">
-        <v>-0.4</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="76" spans="1:6">
       <c r="A76" s="1">
-        <v>45931</v>
+        <v>45870</v>
       </c>
       <c r="B76">
-        <v>-0.51</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="1">
-        <v>45962</v>
+        <v>45901</v>
       </c>
       <c r="B77">
-        <v>-0.55000000000000004</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="1">
+        <v>45931</v>
+      </c>
+      <c r="B78">
+        <v>-0.51</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6">
+      <c r="A79" s="1">
+        <v>45962</v>
+      </c>
+      <c r="B79">
+        <v>-0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6">
+      <c r="A80" s="1">
         <v>45992</v>
       </c>
-      <c r="B78">
+      <c r="B80">
         <v>-0.54</v>
       </c>
     </row>
